--- a/public/imports/493_Pimthong_Logistics.xlsx
+++ b/public/imports/493_Pimthong_Logistics.xlsx
@@ -5,17 +5,17 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phairot P Notebook\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebApp\TSMC\tsmc_web\public\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D584270D-F0B9-434C-BD5F-961CF80634C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AC1142-3586-460A-9D73-178E746CA995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34395" yWindow="1230" windowWidth="19230" windowHeight="10635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -177,7 +177,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="192" formatCode="#############"/>
+    <numFmt numFmtId="164" formatCode="#############"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -279,7 +279,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -289,27 +288,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="192" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -616,7 +616,7 @@
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -624,7 +624,7 @@
     <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
@@ -641,93 +641,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3" t="s">
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
       <c r="R2" s="1" t="s">
         <v>21</v>
       </c>
@@ -746,54 +746,54 @@
       <c r="W2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>25264</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="3">
+        <v>244410</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>2355</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="G3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>69030201</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -834,46 +834,46 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>25266</v>
-      </c>
-      <c r="C4" s="13">
+      <c r="B4" s="3">
+        <v>244412</v>
+      </c>
+      <c r="C4" s="10">
         <v>70</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>6279</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>69030401</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P4" s="2" t="s">
@@ -914,46 +914,46 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>25268</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="3">
+        <v>244414</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>2355</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="G5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>69030601</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P5" s="2" t="s">
@@ -994,46 +994,46 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
-        <v>25270</v>
-      </c>
-      <c r="C6" s="13">
+      <c r="B6" s="3">
+        <v>244416</v>
+      </c>
+      <c r="C6" s="10">
         <v>70</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>6279</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>69030801</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P6" s="2" t="s">
@@ -1074,46 +1074,46 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
-        <v>25272</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="3">
+        <v>244418</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>2355</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="G7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>69031001</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P7" s="2" t="s">
@@ -1154,46 +1154,46 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
-        <v>25274</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="B8" s="3">
+        <v>244420</v>
+      </c>
+      <c r="C8" s="10">
         <v>70</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>6279</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="G8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>69031201</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P8" s="2" t="s">
@@ -1234,46 +1234,46 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
-        <v>25276</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="3">
+        <v>244422</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>2355</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="G9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>69031401</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P9" s="2" t="s">
@@ -1314,46 +1314,46 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
-        <v>25278</v>
-      </c>
-      <c r="C10" s="13">
+      <c r="B10" s="3">
+        <v>244424</v>
+      </c>
+      <c r="C10" s="10">
         <v>70</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>6279</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="G10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>69031601</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P10" s="2" t="s">
@@ -1394,46 +1394,46 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="4">
-        <v>25280</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="3">
+        <v>244426</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>2355</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="G11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>69031801</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P11" s="2" t="s">
@@ -1474,46 +1474,46 @@
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
-        <v>25282</v>
-      </c>
-      <c r="C12" s="13">
+      <c r="B12" s="3">
+        <v>244428</v>
+      </c>
+      <c r="C12" s="10">
         <v>70</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>6279</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="G12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>69032001</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P12" s="2" t="s">
@@ -1554,46 +1554,46 @@
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="4">
-        <v>25284</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="3">
+        <v>244430</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>2355</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="G13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>69032201</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P13" s="2" t="s">
@@ -1634,46 +1634,46 @@
       <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
-        <v>25286</v>
-      </c>
-      <c r="C14" s="13">
+      <c r="B14" s="3">
+        <v>244432</v>
+      </c>
+      <c r="C14" s="10">
         <v>70</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>6279</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="G14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>69032401</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P14" s="2" t="s">
@@ -1714,46 +1714,46 @@
       <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="4">
-        <v>25288</v>
-      </c>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="3">
+        <v>244434</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>2355</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="G15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>69032601</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="2" t="s">
@@ -1794,46 +1794,46 @@
       <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="4">
-        <v>25290</v>
-      </c>
-      <c r="C16" s="13">
+      <c r="B16" s="3">
+        <v>244436</v>
+      </c>
+      <c r="C16" s="10">
         <v>70</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>6279</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="G16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <v>69032801</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P16" s="2" t="s">
@@ -1874,46 +1874,46 @@
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="4">
-        <v>25292</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="3">
+        <v>244438</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>2355</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="G17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>69033001</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P17" s="2" t="s">
@@ -1954,46 +1954,46 @@
       <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="4">
-        <v>25235</v>
-      </c>
-      <c r="C18" s="13">
+      <c r="B18" s="3">
+        <v>244381</v>
+      </c>
+      <c r="C18" s="10">
         <v>70</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>6279</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="G18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>69020101</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P18" s="2" t="s">
@@ -2034,46 +2034,46 @@
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="4">
-        <v>25237</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="3">
+        <v>244383</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>2355</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="G19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>69020301</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O19" s="11" t="s">
+      <c r="O19" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P19" s="2" t="s">
@@ -2114,46 +2114,46 @@
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="4">
-        <v>25239</v>
-      </c>
-      <c r="C20" s="13">
+      <c r="B20" s="3">
+        <v>244385</v>
+      </c>
+      <c r="C20" s="10">
         <v>70</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>6279</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="G20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>69020501</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="M20" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P20" s="2" t="s">
@@ -2194,46 +2194,46 @@
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="4">
-        <v>25241</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="3">
+        <v>244387</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>2355</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="G21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>69020701</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="M21" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P21" s="2" t="s">
@@ -2274,46 +2274,46 @@
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="4">
-        <v>25243</v>
-      </c>
-      <c r="C22" s="13">
+      <c r="B22" s="3">
+        <v>244389</v>
+      </c>
+      <c r="C22" s="10">
         <v>70</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>6279</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="G22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <v>69020901</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="M22" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P22" s="2" t="s">
@@ -2354,46 +2354,46 @@
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="4">
-        <v>25245</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="3">
+        <v>244391</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>2355</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="5" t="s">
+      <c r="G23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>69021101</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="M23" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O23" s="11" t="s">
+      <c r="O23" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P23" s="2" t="s">
@@ -2434,46 +2434,46 @@
       <c r="A24" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="4">
-        <v>25247</v>
-      </c>
-      <c r="C24" s="13">
+      <c r="B24" s="3">
+        <v>244393</v>
+      </c>
+      <c r="C24" s="10">
         <v>70</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>6279</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="G24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>69021301</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M24" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P24" s="2" t="s">
@@ -2514,46 +2514,46 @@
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="4">
-        <v>25249</v>
-      </c>
-      <c r="C25" s="13" t="s">
+      <c r="B25" s="3">
+        <v>244395</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>2355</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="5" t="s">
+      <c r="G25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>69021501</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="M25" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="O25" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P25" s="2" t="s">
@@ -2594,46 +2594,46 @@
       <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="4">
-        <v>25251</v>
-      </c>
-      <c r="C26" s="13">
+      <c r="B26" s="3">
+        <v>244397</v>
+      </c>
+      <c r="C26" s="10">
         <v>70</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>6279</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="G26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="5">
         <v>69021701</v>
       </c>
-      <c r="M26" s="5" t="s">
+      <c r="M26" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O26" s="11" t="s">
+      <c r="O26" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P26" s="2" t="s">
@@ -2674,46 +2674,46 @@
       <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="4">
-        <v>25253</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="B27" s="3">
+        <v>244399</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>2355</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="G27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>69021901</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="M27" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P27" s="2" t="s">
@@ -2754,46 +2754,46 @@
       <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="4">
-        <v>25255</v>
-      </c>
-      <c r="C28" s="13">
+      <c r="B28" s="3">
+        <v>244401</v>
+      </c>
+      <c r="C28" s="10">
         <v>70</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>6279</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="G28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>69022101</v>
       </c>
-      <c r="M28" s="5" t="s">
+      <c r="M28" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O28" s="11" t="s">
+      <c r="O28" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P28" s="2" t="s">
@@ -2834,46 +2834,46 @@
       <c r="A29" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="4">
-        <v>25257</v>
-      </c>
-      <c r="C29" s="13" t="s">
+      <c r="B29" s="3">
+        <v>244403</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>2355</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="G29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>69022301</v>
       </c>
-      <c r="M29" s="5" t="s">
+      <c r="M29" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="O29" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P29" s="2" t="s">
@@ -2914,46 +2914,46 @@
       <c r="A30" s="2">
         <v>28</v>
       </c>
-      <c r="B30" s="4">
-        <v>25259</v>
-      </c>
-      <c r="C30" s="13">
+      <c r="B30" s="3">
+        <v>244405</v>
+      </c>
+      <c r="C30" s="10">
         <v>70</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>6279</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H30" s="5" t="s">
+      <c r="G30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>69022501</v>
       </c>
-      <c r="M30" s="5" t="s">
+      <c r="M30" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O30" s="11" t="s">
+      <c r="O30" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P30" s="2" t="s">
@@ -2994,46 +2994,46 @@
       <c r="A31" s="2">
         <v>29</v>
       </c>
-      <c r="B31" s="4">
-        <v>25261</v>
-      </c>
-      <c r="C31" s="13" t="s">
+      <c r="B31" s="3">
+        <v>244407</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>2355</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I31" s="5" t="s">
+      <c r="G31" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="5">
         <v>69022701</v>
       </c>
-      <c r="M31" s="5" t="s">
+      <c r="M31" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O31" s="11" t="s">
+      <c r="O31" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P31" s="2" t="s">
@@ -3074,46 +3074,46 @@
       <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="4">
-        <v>25205</v>
-      </c>
-      <c r="C32" s="13" t="s">
+      <c r="B32" s="3">
+        <v>244351</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>2355</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="5" t="s">
+      <c r="G32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>69010201</v>
       </c>
-      <c r="M32" s="5" t="s">
+      <c r="M32" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O32" s="11" t="s">
+      <c r="O32" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P32" s="2" t="s">
@@ -3154,46 +3154,46 @@
       <c r="A33" s="2">
         <v>31</v>
       </c>
-      <c r="B33" s="4">
-        <v>25207</v>
-      </c>
-      <c r="C33" s="13">
+      <c r="B33" s="3">
+        <v>244353</v>
+      </c>
+      <c r="C33" s="10">
         <v>70</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>6279</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H33" s="5" t="s">
+      <c r="G33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>69010401</v>
       </c>
-      <c r="M33" s="5" t="s">
+      <c r="M33" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="O33" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P33" s="2" t="s">
@@ -3234,46 +3234,46 @@
       <c r="A34" s="2">
         <v>32</v>
       </c>
-      <c r="B34" s="4">
-        <v>25209</v>
-      </c>
-      <c r="C34" s="13" t="s">
+      <c r="B34" s="3">
+        <v>244355</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>2355</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="5" t="s">
+      <c r="G34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <v>69010601</v>
       </c>
-      <c r="M34" s="5" t="s">
+      <c r="M34" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O34" s="11" t="s">
+      <c r="O34" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P34" s="2" t="s">
@@ -3314,46 +3314,46 @@
       <c r="A35" s="2">
         <v>33</v>
       </c>
-      <c r="B35" s="4">
-        <v>25211</v>
-      </c>
-      <c r="C35" s="13">
+      <c r="B35" s="3">
+        <v>244357</v>
+      </c>
+      <c r="C35" s="10">
         <v>70</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>6279</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H35" s="5" t="s">
+      <c r="G35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>69010801</v>
       </c>
-      <c r="M35" s="5" t="s">
+      <c r="M35" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O35" s="11" t="s">
+      <c r="O35" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P35" s="2" t="s">
@@ -3394,46 +3394,46 @@
       <c r="A36" s="2">
         <v>34</v>
       </c>
-      <c r="B36" s="4">
-        <v>25213</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="3">
+        <v>244359</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="5">
         <v>2355</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" s="5" t="s">
+      <c r="G36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="5">
         <v>69011001</v>
       </c>
-      <c r="M36" s="5" t="s">
+      <c r="M36" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O36" s="11" t="s">
+      <c r="O36" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P36" s="2" t="s">
@@ -3474,46 +3474,46 @@
       <c r="A37" s="2">
         <v>35</v>
       </c>
-      <c r="B37" s="4">
-        <v>25215</v>
-      </c>
-      <c r="C37" s="13">
+      <c r="B37" s="3">
+        <v>244361</v>
+      </c>
+      <c r="C37" s="10">
         <v>70</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>6279</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H37" s="5" t="s">
+      <c r="G37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="5">
         <v>69011201</v>
       </c>
-      <c r="M37" s="5" t="s">
+      <c r="M37" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O37" s="11" t="s">
+      <c r="O37" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P37" s="2" t="s">
@@ -3554,46 +3554,46 @@
       <c r="A38" s="2">
         <v>36</v>
       </c>
-      <c r="B38" s="4">
-        <v>25217</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="3">
+        <v>244363</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="5">
         <v>2355</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="5" t="s">
+      <c r="G38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="5">
         <v>69011401</v>
       </c>
-      <c r="M38" s="5" t="s">
+      <c r="M38" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O38" s="11" t="s">
+      <c r="O38" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P38" s="2" t="s">
@@ -3634,46 +3634,46 @@
       <c r="A39" s="2">
         <v>37</v>
       </c>
-      <c r="B39" s="4">
-        <v>25219</v>
-      </c>
-      <c r="C39" s="13">
+      <c r="B39" s="3">
+        <v>244365</v>
+      </c>
+      <c r="C39" s="10">
         <v>70</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>6279</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H39" s="5" t="s">
+      <c r="G39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="5">
         <v>69011601</v>
       </c>
-      <c r="M39" s="5" t="s">
+      <c r="M39" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O39" s="11" t="s">
+      <c r="O39" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="2" t="s">
@@ -3714,46 +3714,46 @@
       <c r="A40" s="2">
         <v>38</v>
       </c>
-      <c r="B40" s="4">
-        <v>25221</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="B40" s="3">
+        <v>244367</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>2355</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I40" s="5" t="s">
+      <c r="G40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>69011801</v>
       </c>
-      <c r="M40" s="5" t="s">
+      <c r="M40" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O40" s="11" t="s">
+      <c r="O40" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P40" s="2" t="s">
@@ -3794,46 +3794,46 @@
       <c r="A41" s="2">
         <v>39</v>
       </c>
-      <c r="B41" s="4">
-        <v>25223</v>
-      </c>
-      <c r="C41" s="13">
+      <c r="B41" s="3">
+        <v>244369</v>
+      </c>
+      <c r="C41" s="10">
         <v>70</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>6279</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="G41" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>69012001</v>
       </c>
-      <c r="M41" s="5" t="s">
+      <c r="M41" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O41" s="11" t="s">
+      <c r="O41" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P41" s="2" t="s">
@@ -3874,46 +3874,46 @@
       <c r="A42" s="2">
         <v>40</v>
       </c>
-      <c r="B42" s="4">
-        <v>25225</v>
-      </c>
-      <c r="C42" s="13" t="s">
+      <c r="B42" s="3">
+        <v>244371</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>2355</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="5" t="s">
+      <c r="G42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="5">
         <v>69012201</v>
       </c>
-      <c r="M42" s="5" t="s">
+      <c r="M42" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O42" s="11" t="s">
+      <c r="O42" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P42" s="2" t="s">
@@ -3954,46 +3954,46 @@
       <c r="A43" s="2">
         <v>41</v>
       </c>
-      <c r="B43" s="4">
-        <v>25227</v>
-      </c>
-      <c r="C43" s="13">
+      <c r="B43" s="3">
+        <v>244373</v>
+      </c>
+      <c r="C43" s="10">
         <v>70</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="5">
         <v>6279</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H43" s="5" t="s">
+      <c r="G43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="J43" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="5">
         <v>69012401</v>
       </c>
-      <c r="M43" s="5" t="s">
+      <c r="M43" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P43" s="2" t="s">
@@ -4034,46 +4034,46 @@
       <c r="A44" s="2">
         <v>42</v>
       </c>
-      <c r="B44" s="4">
-        <v>25229</v>
-      </c>
-      <c r="C44" s="13" t="s">
+      <c r="B44" s="3">
+        <v>244375</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>2355</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="5" t="s">
+      <c r="G44" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="10">
+      <c r="K44" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="5">
         <v>69012601</v>
       </c>
-      <c r="M44" s="5" t="s">
+      <c r="M44" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O44" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P44" s="2" t="s">
@@ -4114,46 +4114,46 @@
       <c r="A45" s="2">
         <v>43</v>
       </c>
-      <c r="B45" s="4">
-        <v>25231</v>
-      </c>
-      <c r="C45" s="13">
+      <c r="B45" s="3">
+        <v>244377</v>
+      </c>
+      <c r="C45" s="10">
         <v>70</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="5">
         <v>6279</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H45" s="5" t="s">
+      <c r="G45" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="I45" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J45" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="5">
         <v>69012801</v>
       </c>
-      <c r="M45" s="5" t="s">
+      <c r="M45" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P45" s="2" t="s">
@@ -4194,46 +4194,46 @@
       <c r="A46" s="2">
         <v>44</v>
       </c>
-      <c r="B46" s="4">
-        <v>25233</v>
-      </c>
-      <c r="C46" s="13" t="s">
+      <c r="B46" s="3">
+        <v>244379</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>2355</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="5" t="s">
+      <c r="G46" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>69013001</v>
       </c>
-      <c r="M46" s="5" t="s">
+      <c r="M46" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O46" s="11" t="s">
+      <c r="O46" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P46" s="2" t="s">
@@ -4274,46 +4274,46 @@
       <c r="A47" s="2">
         <v>45</v>
       </c>
-      <c r="B47" s="4">
-        <v>25173</v>
-      </c>
-      <c r="C47" s="13" t="s">
+      <c r="B47" s="3">
+        <v>244319</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>2355</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="5" t="s">
+      <c r="G47" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K47" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>68120101</v>
       </c>
-      <c r="M47" s="5" t="s">
+      <c r="M47" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O47" s="11" t="s">
+      <c r="O47" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P47" s="2" t="s">
@@ -4354,46 +4354,46 @@
       <c r="A48" s="2">
         <v>46</v>
       </c>
-      <c r="B48" s="4">
-        <v>25175</v>
-      </c>
-      <c r="C48" s="13">
+      <c r="B48" s="3">
+        <v>244321</v>
+      </c>
+      <c r="C48" s="10">
         <v>70</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>6279</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H48" s="5" t="s">
+      <c r="G48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="I48" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K48" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>68120301</v>
       </c>
-      <c r="M48" s="5" t="s">
+      <c r="M48" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O48" s="11" t="s">
+      <c r="O48" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P48" s="2" t="s">
@@ -4434,46 +4434,46 @@
       <c r="A49" s="2">
         <v>47</v>
       </c>
-      <c r="B49" s="4">
-        <v>25177</v>
-      </c>
-      <c r="C49" s="13" t="s">
+      <c r="B49" s="3">
+        <v>244323</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>2355</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="5" t="s">
+      <c r="G49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K49" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="5">
         <v>68120501</v>
       </c>
-      <c r="M49" s="5" t="s">
+      <c r="M49" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O49" s="11" t="s">
+      <c r="O49" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P49" s="2" t="s">
@@ -4514,46 +4514,46 @@
       <c r="A50" s="2">
         <v>48</v>
       </c>
-      <c r="B50" s="4">
-        <v>25179</v>
-      </c>
-      <c r="C50" s="13">
+      <c r="B50" s="3">
+        <v>244325</v>
+      </c>
+      <c r="C50" s="10">
         <v>70</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>6279</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H50" s="5" t="s">
+      <c r="G50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="I50" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K50" s="10">
+      <c r="K50" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="5">
         <v>68120701</v>
       </c>
-      <c r="M50" s="5" t="s">
+      <c r="M50" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O50" s="11" t="s">
+      <c r="O50" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P50" s="2" t="s">
@@ -4594,46 +4594,46 @@
       <c r="A51" s="2">
         <v>49</v>
       </c>
-      <c r="B51" s="4">
-        <v>25181</v>
-      </c>
-      <c r="C51" s="13" t="s">
+      <c r="B51" s="3">
+        <v>244327</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>2355</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I51" s="5" t="s">
+      <c r="G51" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I51" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="5" t="s">
+      <c r="J51" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="8">
         <v>1710500246655</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>68120901</v>
       </c>
-      <c r="M51" s="5" t="s">
+      <c r="M51" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P51" s="2" t="s">
@@ -4674,46 +4674,46 @@
       <c r="A52" s="2">
         <v>50</v>
       </c>
-      <c r="B52" s="4">
-        <v>25183</v>
-      </c>
-      <c r="C52" s="13">
+      <c r="B52" s="3">
+        <v>244329</v>
+      </c>
+      <c r="C52" s="10">
         <v>70</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>6279</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H52" s="5" t="s">
+      <c r="G52" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H52" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I52" s="5" t="s">
+      <c r="I52" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="5" t="s">
+      <c r="J52" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K52" s="8">
         <v>1102003229903</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52" s="5">
         <v>68121101</v>
       </c>
-      <c r="M52" s="5" t="s">
+      <c r="M52" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="O52" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P52" s="2" t="s">
@@ -4754,46 +4754,46 @@
       <c r="A53" s="2">
         <v>51</v>
       </c>
-      <c r="B53" s="4">
-        <v>25185</v>
-      </c>
-      <c r="C53" s="13" t="s">
+      <c r="B53" s="3">
+        <v>244331</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="5">
         <v>2355</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I53" s="5" t="s">
+      <c r="G53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J53" s="5" t="s">
+      <c r="J53" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K53" s="8" t="s">
+      <c r="K53" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="5">
         <v>68121301</v>
       </c>
-      <c r="M53" s="5" t="s">
+      <c r="M53" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P53" s="2" t="s">
@@ -4834,46 +4834,46 @@
       <c r="A54" s="2">
         <v>52</v>
       </c>
-      <c r="B54" s="4">
-        <v>25187</v>
-      </c>
-      <c r="C54" s="13">
+      <c r="B54" s="3">
+        <v>244333</v>
+      </c>
+      <c r="C54" s="10">
         <v>70</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="5">
         <v>6279</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H54" s="5" t="s">
+      <c r="G54" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I54" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K54" s="8" t="s">
+      <c r="K54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="5">
         <v>68121501</v>
       </c>
-      <c r="M54" s="5" t="s">
+      <c r="M54" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O54" s="11" t="s">
+      <c r="O54" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P54" s="2" t="s">
@@ -4914,46 +4914,46 @@
       <c r="A55" s="2">
         <v>53</v>
       </c>
-      <c r="B55" s="4">
-        <v>25189</v>
-      </c>
-      <c r="C55" s="13" t="s">
+      <c r="B55" s="3">
+        <v>244335</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="5">
         <v>2355</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I55" s="5" t="s">
+      <c r="G55" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="J55" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="8" t="s">
+      <c r="K55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="5">
         <v>68121701</v>
       </c>
-      <c r="M55" s="5" t="s">
+      <c r="M55" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O55" s="11" t="s">
+      <c r="O55" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P55" s="2" t="s">
@@ -4994,46 +4994,46 @@
       <c r="A56" s="2">
         <v>54</v>
       </c>
-      <c r="B56" s="4">
-        <v>25191</v>
-      </c>
-      <c r="C56" s="13">
+      <c r="B56" s="3">
+        <v>244337</v>
+      </c>
+      <c r="C56" s="10">
         <v>70</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="5">
         <v>6279</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H56" s="5" t="s">
+      <c r="G56" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="I56" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="8" t="s">
+      <c r="K56" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="5">
         <v>68121901</v>
       </c>
-      <c r="M56" s="5" t="s">
+      <c r="M56" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O56" s="11" t="s">
+      <c r="O56" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P56" s="2" t="s">
@@ -5074,46 +5074,46 @@
       <c r="A57" s="2">
         <v>55</v>
       </c>
-      <c r="B57" s="4">
-        <v>25193</v>
-      </c>
-      <c r="C57" s="13" t="s">
+      <c r="B57" s="3">
+        <v>244339</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="5">
         <v>2355</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I57" s="5" t="s">
+      <c r="G57" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="J57" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K57" s="8" t="s">
+      <c r="K57" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L57" s="6">
+      <c r="L57" s="5">
         <v>68122101</v>
       </c>
-      <c r="M57" s="5" t="s">
+      <c r="M57" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O57" s="11" t="s">
+      <c r="O57" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P57" s="2" t="s">
@@ -5154,46 +5154,46 @@
       <c r="A58" s="2">
         <v>56</v>
       </c>
-      <c r="B58" s="4">
-        <v>25195</v>
-      </c>
-      <c r="C58" s="13">
+      <c r="B58" s="3">
+        <v>244341</v>
+      </c>
+      <c r="C58" s="10">
         <v>70</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="5">
         <v>6279</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H58" s="5" t="s">
+      <c r="G58" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H58" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="I58" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="8" t="s">
+      <c r="K58" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="5">
         <v>68122301</v>
       </c>
-      <c r="M58" s="5" t="s">
+      <c r="M58" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O58" s="11" t="s">
+      <c r="O58" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P58" s="2" t="s">
@@ -5234,46 +5234,46 @@
       <c r="A59" s="2">
         <v>57</v>
       </c>
-      <c r="B59" s="4">
-        <v>25197</v>
-      </c>
-      <c r="C59" s="13" t="s">
+      <c r="B59" s="3">
+        <v>244343</v>
+      </c>
+      <c r="C59" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="5">
         <v>2355</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I59" s="5" t="s">
+      <c r="G59" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K59" s="8" t="s">
+      <c r="K59" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="5">
         <v>68122501</v>
       </c>
-      <c r="M59" s="5" t="s">
+      <c r="M59" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O59" s="11" t="s">
+      <c r="O59" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P59" s="2" t="s">
@@ -5314,46 +5314,46 @@
       <c r="A60" s="2">
         <v>58</v>
       </c>
-      <c r="B60" s="4">
-        <v>25199</v>
-      </c>
-      <c r="C60" s="13">
+      <c r="B60" s="3">
+        <v>244345</v>
+      </c>
+      <c r="C60" s="10">
         <v>70</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="5">
         <v>6279</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H60" s="5" t="s">
+      <c r="G60" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I60" s="5" t="s">
+      <c r="I60" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J60" s="5" t="s">
+      <c r="J60" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K60" s="8" t="s">
+      <c r="K60" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="5">
         <v>68122701</v>
       </c>
-      <c r="M60" s="5" t="s">
+      <c r="M60" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O60" s="11" t="s">
+      <c r="O60" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P60" s="2" t="s">
@@ -5394,46 +5394,46 @@
       <c r="A61" s="2">
         <v>59</v>
       </c>
-      <c r="B61" s="4">
-        <v>25201</v>
-      </c>
-      <c r="C61" s="13" t="s">
+      <c r="B61" s="3">
+        <v>244347</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="5">
         <v>2355</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I61" s="5" t="s">
+      <c r="G61" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J61" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K61" s="8" t="s">
+      <c r="K61" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="5">
         <v>68122901</v>
       </c>
-      <c r="M61" s="5" t="s">
+      <c r="M61" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O61" s="11" t="s">
+      <c r="O61" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P61" s="2" t="s">
@@ -5474,46 +5474,46 @@
       <c r="A62" s="2">
         <v>60</v>
       </c>
-      <c r="B62" s="4">
-        <v>25144</v>
-      </c>
-      <c r="C62" s="13">
+      <c r="B62" s="3">
+        <v>244290</v>
+      </c>
+      <c r="C62" s="10">
         <v>70</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="5">
         <v>6279</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H62" s="5" t="s">
+      <c r="G62" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I62" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J62" s="5" t="s">
+      <c r="J62" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K62" s="8" t="s">
+      <c r="K62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="5">
         <v>68110201</v>
       </c>
-      <c r="M62" s="5" t="s">
+      <c r="M62" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O62" s="11" t="s">
+      <c r="O62" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P62" s="2" t="s">
@@ -5554,46 +5554,46 @@
       <c r="A63" s="2">
         <v>61</v>
       </c>
-      <c r="B63" s="4">
-        <v>25146</v>
-      </c>
-      <c r="C63" s="13" t="s">
+      <c r="B63" s="3">
+        <v>244292</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="5">
         <v>2355</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I63" s="5" t="s">
+      <c r="G63" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J63" s="5" t="s">
+      <c r="J63" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K63" s="8" t="s">
+      <c r="K63" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L63" s="6">
+      <c r="L63" s="5">
         <v>68110401</v>
       </c>
-      <c r="M63" s="5" t="s">
+      <c r="M63" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O63" s="11" t="s">
+      <c r="O63" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P63" s="2" t="s">
@@ -5634,46 +5634,46 @@
       <c r="A64" s="2">
         <v>62</v>
       </c>
-      <c r="B64" s="4">
-        <v>25148</v>
-      </c>
-      <c r="C64" s="13">
+      <c r="B64" s="3">
+        <v>244294</v>
+      </c>
+      <c r="C64" s="10">
         <v>70</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="5">
         <v>6279</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H64" s="5" t="s">
+      <c r="G64" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I64" s="5" t="s">
+      <c r="I64" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K64" s="8" t="s">
+      <c r="K64" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L64" s="6">
+      <c r="L64" s="5">
         <v>68110601</v>
       </c>
-      <c r="M64" s="5" t="s">
+      <c r="M64" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O64" s="11" t="s">
+      <c r="O64" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P64" s="2" t="s">
@@ -5714,46 +5714,46 @@
       <c r="A65" s="2">
         <v>63</v>
       </c>
-      <c r="B65" s="4">
-        <v>25150</v>
-      </c>
-      <c r="C65" s="13" t="s">
+      <c r="B65" s="3">
+        <v>244296</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="5">
         <v>2355</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I65" s="5" t="s">
+      <c r="G65" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J65" s="5" t="s">
+      <c r="J65" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K65" s="8" t="s">
+      <c r="K65" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <v>68110801</v>
       </c>
-      <c r="M65" s="5" t="s">
+      <c r="M65" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O65" s="11" t="s">
+      <c r="O65" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P65" s="2" t="s">
@@ -5794,46 +5794,46 @@
       <c r="A66" s="2">
         <v>64</v>
       </c>
-      <c r="B66" s="4">
-        <v>25152</v>
-      </c>
-      <c r="C66" s="13">
+      <c r="B66" s="3">
+        <v>244298</v>
+      </c>
+      <c r="C66" s="10">
         <v>70</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="5">
         <v>6279</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H66" s="5" t="s">
+      <c r="G66" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="I66" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J66" s="5" t="s">
+      <c r="J66" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K66" s="8" t="s">
+      <c r="K66" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <v>68111001</v>
       </c>
-      <c r="M66" s="5" t="s">
+      <c r="M66" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O66" s="11" t="s">
+      <c r="O66" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P66" s="2" t="s">
@@ -5874,46 +5874,46 @@
       <c r="A67" s="2">
         <v>65</v>
       </c>
-      <c r="B67" s="4">
-        <v>25154</v>
-      </c>
-      <c r="C67" s="13" t="s">
+      <c r="B67" s="3">
+        <v>244300</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="5">
         <v>2355</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I67" s="5" t="s">
+      <c r="G67" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J67" s="5" t="s">
+      <c r="J67" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K67" s="8" t="s">
+      <c r="K67" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="5">
         <v>68111201</v>
       </c>
-      <c r="M67" s="5" t="s">
+      <c r="M67" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O67" s="11" t="s">
+      <c r="O67" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P67" s="2" t="s">
@@ -5954,46 +5954,46 @@
       <c r="A68" s="2">
         <v>66</v>
       </c>
-      <c r="B68" s="4">
-        <v>25156</v>
-      </c>
-      <c r="C68" s="13">
+      <c r="B68" s="3">
+        <v>244302</v>
+      </c>
+      <c r="C68" s="10">
         <v>70</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="5">
         <v>6279</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H68" s="5" t="s">
+      <c r="G68" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="I68" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J68" s="5" t="s">
+      <c r="J68" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K68" s="8" t="s">
+      <c r="K68" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <v>68111401</v>
       </c>
-      <c r="M68" s="5" t="s">
+      <c r="M68" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O68" s="11" t="s">
+      <c r="O68" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P68" s="2" t="s">
@@ -6034,46 +6034,46 @@
       <c r="A69" s="2">
         <v>67</v>
       </c>
-      <c r="B69" s="4">
-        <v>25158</v>
-      </c>
-      <c r="C69" s="13" t="s">
+      <c r="B69" s="3">
+        <v>244304</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="5">
         <v>2355</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I69" s="5" t="s">
+      <c r="G69" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J69" s="5" t="s">
+      <c r="J69" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K69" s="8" t="s">
+      <c r="K69" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="5">
         <v>68111601</v>
       </c>
-      <c r="M69" s="5" t="s">
+      <c r="M69" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O69" s="11" t="s">
+      <c r="O69" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P69" s="2" t="s">
@@ -6114,46 +6114,46 @@
       <c r="A70" s="2">
         <v>68</v>
       </c>
-      <c r="B70" s="4">
-        <v>25160</v>
-      </c>
-      <c r="C70" s="13">
+      <c r="B70" s="3">
+        <v>244306</v>
+      </c>
+      <c r="C70" s="10">
         <v>70</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="5">
         <v>6279</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H70" s="5" t="s">
+      <c r="G70" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I70" s="5" t="s">
+      <c r="I70" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J70" s="5" t="s">
+      <c r="J70" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K70" s="8" t="s">
+      <c r="K70" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="5">
         <v>68111801</v>
       </c>
-      <c r="M70" s="5" t="s">
+      <c r="M70" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O70" s="11" t="s">
+      <c r="O70" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P70" s="2" t="s">
@@ -6194,46 +6194,46 @@
       <c r="A71" s="2">
         <v>69</v>
       </c>
-      <c r="B71" s="4">
-        <v>25162</v>
-      </c>
-      <c r="C71" s="13" t="s">
+      <c r="B71" s="3">
+        <v>244308</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="5">
         <v>2355</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I71" s="5" t="s">
+      <c r="G71" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J71" s="5" t="s">
+      <c r="J71" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K71" s="8" t="s">
+      <c r="K71" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L71" s="6">
+      <c r="L71" s="5">
         <v>68112001</v>
       </c>
-      <c r="M71" s="5" t="s">
+      <c r="M71" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O71" s="11" t="s">
+      <c r="O71" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P71" s="2" t="s">
@@ -6274,46 +6274,46 @@
       <c r="A72" s="2">
         <v>70</v>
       </c>
-      <c r="B72" s="4">
-        <v>25164</v>
-      </c>
-      <c r="C72" s="13">
+      <c r="B72" s="3">
+        <v>244310</v>
+      </c>
+      <c r="C72" s="10">
         <v>70</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="5">
         <v>6279</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G72" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H72" s="5" t="s">
+      <c r="G72" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I72" s="5" t="s">
+      <c r="I72" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K72" s="8" t="s">
+      <c r="K72" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="5">
         <v>68112201</v>
       </c>
-      <c r="M72" s="5" t="s">
+      <c r="M72" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O72" s="11" t="s">
+      <c r="O72" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P72" s="2" t="s">
@@ -6354,46 +6354,46 @@
       <c r="A73" s="2">
         <v>71</v>
       </c>
-      <c r="B73" s="4">
-        <v>25166</v>
-      </c>
-      <c r="C73" s="13" t="s">
+      <c r="B73" s="3">
+        <v>244312</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="5">
         <v>2355</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I73" s="5" t="s">
+      <c r="G73" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J73" s="5" t="s">
+      <c r="J73" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K73" s="8" t="s">
+      <c r="K73" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="5">
         <v>68112401</v>
       </c>
-      <c r="M73" s="5" t="s">
+      <c r="M73" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O73" s="11" t="s">
+      <c r="O73" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P73" s="2" t="s">
@@ -6434,46 +6434,46 @@
       <c r="A74" s="2">
         <v>72</v>
       </c>
-      <c r="B74" s="4">
-        <v>25168</v>
-      </c>
-      <c r="C74" s="13">
+      <c r="B74" s="3">
+        <v>244314</v>
+      </c>
+      <c r="C74" s="10">
         <v>70</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="5">
         <v>6279</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H74" s="5" t="s">
+      <c r="G74" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I74" s="5" t="s">
+      <c r="I74" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="J74" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K74" s="8" t="s">
+      <c r="K74" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="5">
         <v>68112601</v>
       </c>
-      <c r="M74" s="5" t="s">
+      <c r="M74" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O74" s="11" t="s">
+      <c r="O74" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P74" s="2" t="s">
@@ -6514,46 +6514,46 @@
       <c r="A75" s="2">
         <v>73</v>
       </c>
-      <c r="B75" s="4">
-        <v>25170</v>
-      </c>
-      <c r="C75" s="13" t="s">
+      <c r="B75" s="3">
+        <v>244316</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="5">
         <v>2355</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I75" s="5" t="s">
+      <c r="G75" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I75" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J75" s="5" t="s">
+      <c r="J75" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K75" s="8" t="s">
+      <c r="K75" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="5">
         <v>68112801</v>
       </c>
-      <c r="M75" s="5" t="s">
+      <c r="M75" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O75" s="11" t="s">
+      <c r="O75" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P75" s="2" t="s">
@@ -6594,46 +6594,46 @@
       <c r="A76" s="2">
         <v>74</v>
       </c>
-      <c r="B76" s="4">
-        <v>25172</v>
-      </c>
-      <c r="C76" s="13">
+      <c r="B76" s="3">
+        <v>244318</v>
+      </c>
+      <c r="C76" s="10">
         <v>70</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76" s="5">
         <v>6279</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H76" s="5" t="s">
+      <c r="G76" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="I76" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J76" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K76" s="8" t="s">
+      <c r="K76" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="5">
         <v>68113001</v>
       </c>
-      <c r="M76" s="5" t="s">
+      <c r="M76" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O76" s="11" t="s">
+      <c r="O76" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P76" s="2" t="s">
@@ -6674,46 +6674,46 @@
       <c r="A77" s="2">
         <v>75</v>
       </c>
-      <c r="B77" s="4">
-        <v>25112</v>
-      </c>
-      <c r="C77" s="13" t="s">
+      <c r="B77" s="3">
+        <v>244258</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="5">
         <v>2355</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I77" s="5" t="s">
+      <c r="G77" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I77" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J77" s="5" t="s">
+      <c r="J77" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K77" s="8" t="s">
+      <c r="K77" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L77" s="6">
+      <c r="L77" s="5">
         <v>68100101</v>
       </c>
-      <c r="M77" s="5" t="s">
+      <c r="M77" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O77" s="11" t="s">
+      <c r="O77" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P77" s="2" t="s">
@@ -6754,46 +6754,46 @@
       <c r="A78" s="2">
         <v>76</v>
       </c>
-      <c r="B78" s="4">
-        <v>25114</v>
-      </c>
-      <c r="C78" s="13">
+      <c r="B78" s="3">
+        <v>244260</v>
+      </c>
+      <c r="C78" s="10">
         <v>70</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78" s="5">
         <v>6279</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H78" s="5" t="s">
+      <c r="G78" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H78" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="I78" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J78" s="5" t="s">
+      <c r="J78" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K78" s="8" t="s">
+      <c r="K78" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="5">
         <v>68100301</v>
       </c>
-      <c r="M78" s="5" t="s">
+      <c r="M78" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O78" s="11" t="s">
+      <c r="O78" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P78" s="2" t="s">
@@ -6834,46 +6834,46 @@
       <c r="A79" s="2">
         <v>77</v>
       </c>
-      <c r="B79" s="4">
-        <v>25116</v>
-      </c>
-      <c r="C79" s="13" t="s">
+      <c r="B79" s="3">
+        <v>244262</v>
+      </c>
+      <c r="C79" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="5">
         <v>2355</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I79" s="5" t="s">
+      <c r="G79" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J79" s="5" t="s">
+      <c r="J79" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K79" s="8" t="s">
+      <c r="K79" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L79" s="6">
+      <c r="L79" s="5">
         <v>68100501</v>
       </c>
-      <c r="M79" s="5" t="s">
+      <c r="M79" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O79" s="11" t="s">
+      <c r="O79" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P79" s="2" t="s">
@@ -6914,46 +6914,46 @@
       <c r="A80" s="2">
         <v>78</v>
       </c>
-      <c r="B80" s="4">
-        <v>25118</v>
-      </c>
-      <c r="C80" s="13">
+      <c r="B80" s="3">
+        <v>244264</v>
+      </c>
+      <c r="C80" s="10">
         <v>70</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="5">
         <v>6279</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H80" s="5" t="s">
+      <c r="G80" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H80" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I80" s="5" t="s">
+      <c r="I80" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J80" s="5" t="s">
+      <c r="J80" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K80" s="8" t="s">
+      <c r="K80" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L80" s="6">
+      <c r="L80" s="5">
         <v>68100701</v>
       </c>
-      <c r="M80" s="5" t="s">
+      <c r="M80" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O80" s="11" t="s">
+      <c r="O80" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P80" s="2" t="s">
@@ -6994,46 +6994,46 @@
       <c r="A81" s="2">
         <v>79</v>
       </c>
-      <c r="B81" s="4">
-        <v>25120</v>
-      </c>
-      <c r="C81" s="13" t="s">
+      <c r="B81" s="3">
+        <v>244266</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D81" s="5">
         <v>2355</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G81" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I81" s="5" t="s">
+      <c r="G81" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J81" s="5" t="s">
+      <c r="J81" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K81" s="8" t="s">
+      <c r="K81" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L81" s="6">
+      <c r="L81" s="5">
         <v>68100901</v>
       </c>
-      <c r="M81" s="5" t="s">
+      <c r="M81" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O81" s="11" t="s">
+      <c r="O81" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P81" s="2" t="s">
@@ -7074,46 +7074,46 @@
       <c r="A82" s="2">
         <v>80</v>
       </c>
-      <c r="B82" s="4">
-        <v>25122</v>
-      </c>
-      <c r="C82" s="13">
+      <c r="B82" s="3">
+        <v>244268</v>
+      </c>
+      <c r="C82" s="10">
         <v>70</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D82" s="5">
         <v>6279</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H82" s="5" t="s">
+      <c r="G82" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I82" s="5" t="s">
+      <c r="I82" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J82" s="5" t="s">
+      <c r="J82" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K82" s="8" t="s">
+      <c r="K82" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L82" s="6">
+      <c r="L82" s="5">
         <v>68101101</v>
       </c>
-      <c r="M82" s="5" t="s">
+      <c r="M82" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O82" s="11" t="s">
+      <c r="O82" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P82" s="2" t="s">
@@ -7154,46 +7154,46 @@
       <c r="A83" s="2">
         <v>81</v>
       </c>
-      <c r="B83" s="4">
-        <v>25124</v>
-      </c>
-      <c r="C83" s="13" t="s">
+      <c r="B83" s="3">
+        <v>244270</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="5">
         <v>2355</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E83" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I83" s="5" t="s">
+      <c r="G83" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I83" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J83" s="5" t="s">
+      <c r="J83" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K83" s="8" t="s">
+      <c r="K83" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L83" s="6">
+      <c r="L83" s="5">
         <v>68101301</v>
       </c>
-      <c r="M83" s="5" t="s">
+      <c r="M83" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O83" s="11" t="s">
+      <c r="O83" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P83" s="2" t="s">
@@ -7234,46 +7234,46 @@
       <c r="A84" s="2">
         <v>82</v>
       </c>
-      <c r="B84" s="4">
-        <v>25126</v>
-      </c>
-      <c r="C84" s="13">
+      <c r="B84" s="3">
+        <v>244272</v>
+      </c>
+      <c r="C84" s="10">
         <v>70</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="5">
         <v>6279</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H84" s="5" t="s">
+      <c r="G84" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H84" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I84" s="5" t="s">
+      <c r="I84" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J84" s="5" t="s">
+      <c r="J84" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K84" s="8" t="s">
+      <c r="K84" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="5">
         <v>68101501</v>
       </c>
-      <c r="M84" s="5" t="s">
+      <c r="M84" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O84" s="11" t="s">
+      <c r="O84" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P84" s="2" t="s">
@@ -7314,46 +7314,46 @@
       <c r="A85" s="2">
         <v>83</v>
       </c>
-      <c r="B85" s="4">
-        <v>25128</v>
-      </c>
-      <c r="C85" s="13" t="s">
+      <c r="B85" s="3">
+        <v>244274</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="5">
         <v>2355</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I85" s="5" t="s">
+      <c r="G85" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J85" s="5" t="s">
+      <c r="J85" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K85" s="8" t="s">
+      <c r="K85" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L85" s="6">
+      <c r="L85" s="5">
         <v>68101701</v>
       </c>
-      <c r="M85" s="5" t="s">
+      <c r="M85" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O85" s="11" t="s">
+      <c r="O85" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P85" s="2" t="s">
@@ -7394,46 +7394,46 @@
       <c r="A86" s="2">
         <v>84</v>
       </c>
-      <c r="B86" s="4">
-        <v>25130</v>
-      </c>
-      <c r="C86" s="13">
+      <c r="B86" s="3">
+        <v>244276</v>
+      </c>
+      <c r="C86" s="10">
         <v>70</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="5">
         <v>6279</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H86" s="5" t="s">
+      <c r="G86" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I86" s="5" t="s">
+      <c r="I86" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J86" s="5" t="s">
+      <c r="J86" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K86" s="8" t="s">
+      <c r="K86" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L86" s="6">
+      <c r="L86" s="5">
         <v>68101901</v>
       </c>
-      <c r="M86" s="5" t="s">
+      <c r="M86" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O86" s="11" t="s">
+      <c r="O86" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P86" s="2" t="s">
@@ -7474,46 +7474,46 @@
       <c r="A87" s="2">
         <v>85</v>
       </c>
-      <c r="B87" s="4">
-        <v>25132</v>
-      </c>
-      <c r="C87" s="13" t="s">
+      <c r="B87" s="3">
+        <v>244278</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="5">
         <v>2355</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H87" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I87" s="5" t="s">
+      <c r="G87" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I87" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J87" s="5" t="s">
+      <c r="J87" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K87" s="8" t="s">
+      <c r="K87" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="5">
         <v>68102101</v>
       </c>
-      <c r="M87" s="5" t="s">
+      <c r="M87" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O87" s="11" t="s">
+      <c r="O87" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P87" s="2" t="s">
@@ -7554,46 +7554,46 @@
       <c r="A88" s="2">
         <v>86</v>
       </c>
-      <c r="B88" s="4">
-        <v>25134</v>
-      </c>
-      <c r="C88" s="13">
+      <c r="B88" s="3">
+        <v>244280</v>
+      </c>
+      <c r="C88" s="10">
         <v>70</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="5">
         <v>6279</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H88" s="5" t="s">
+      <c r="G88" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I88" s="5" t="s">
+      <c r="I88" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J88" s="5" t="s">
+      <c r="J88" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K88" s="8" t="s">
+      <c r="K88" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L88" s="6">
+      <c r="L88" s="5">
         <v>68102301</v>
       </c>
-      <c r="M88" s="5" t="s">
+      <c r="M88" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O88" s="11" t="s">
+      <c r="O88" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P88" s="2" t="s">
@@ -7634,46 +7634,46 @@
       <c r="A89" s="2">
         <v>87</v>
       </c>
-      <c r="B89" s="4">
-        <v>25136</v>
-      </c>
-      <c r="C89" s="13" t="s">
+      <c r="B89" s="3">
+        <v>244282</v>
+      </c>
+      <c r="C89" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="5">
         <v>2355</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I89" s="5" t="s">
+      <c r="G89" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J89" s="5" t="s">
+      <c r="J89" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K89" s="8" t="s">
+      <c r="K89" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L89" s="6">
+      <c r="L89" s="5">
         <v>68102501</v>
       </c>
-      <c r="M89" s="5" t="s">
+      <c r="M89" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O89" s="11" t="s">
+      <c r="O89" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P89" s="2" t="s">
@@ -7714,46 +7714,46 @@
       <c r="A90" s="2">
         <v>88</v>
       </c>
-      <c r="B90" s="4">
-        <v>25138</v>
-      </c>
-      <c r="C90" s="13">
+      <c r="B90" s="3">
+        <v>244284</v>
+      </c>
+      <c r="C90" s="10">
         <v>70</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="5">
         <v>6279</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E90" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G90" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H90" s="5" t="s">
+      <c r="G90" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I90" s="5" t="s">
+      <c r="I90" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J90" s="5" t="s">
+      <c r="J90" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K90" s="8" t="s">
+      <c r="K90" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L90" s="6">
+      <c r="L90" s="5">
         <v>68102701</v>
       </c>
-      <c r="M90" s="5" t="s">
+      <c r="M90" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O90" s="11" t="s">
+      <c r="O90" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P90" s="2" t="s">
@@ -7794,46 +7794,46 @@
       <c r="A91" s="2">
         <v>89</v>
       </c>
-      <c r="B91" s="4">
-        <v>25140</v>
-      </c>
-      <c r="C91" s="13" t="s">
+      <c r="B91" s="3">
+        <v>244286</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="5">
         <v>2355</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="E91" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I91" s="5" t="s">
+      <c r="G91" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J91" s="5" t="s">
+      <c r="J91" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K91" s="8" t="s">
+      <c r="K91" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L91" s="6">
+      <c r="L91" s="5">
         <v>68102901</v>
       </c>
-      <c r="M91" s="5" t="s">
+      <c r="M91" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O91" s="11" t="s">
+      <c r="O91" s="9" t="s">
         <v>49</v>
       </c>
       <c r="P91" s="2" t="s">
@@ -7872,16 +7872,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
@@ -7893,6 +7883,16 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
